--- a/antares/twin/docs/Відомість_фото_обстеження_Антарес_26-27.10.2026.xlsx
+++ b/antares/twin/docs/Відомість_фото_обстеження_Антарес_26-27.10.2026.xlsx
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I52" s="4" t="n">
@@ -4038,7 +4038,7 @@
       <c r="M52" s="4" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I81" s="7" t="n">
@@ -6068,7 +6068,7 @@
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O81" s="7" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I82" s="4" t="n">
@@ -6138,7 +6138,7 @@
       <c r="M82" s="4" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
@@ -6258,11 +6258,11 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>22</v>
@@ -6278,7 +6278,7 @@
       <c r="M84" s="4" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I85" s="7" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J85" s="7" t="n">
         <v>30</v>
@@ -6348,7 +6348,7 @@
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O85" s="7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I86" s="4" t="n">
@@ -6418,7 +6418,7 @@
       <c r="M86" s="4" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -6468,27 +6468,27 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I87" s="7" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K87" s="7" t="n">
         <v>295</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>З даху АБК на захід: парапет АБК, нижче дах ТП-5913, стіна цеху з вікнами; над нею дах цеху — рама кондиціонерів, дефлектори, ліхтарі. Кругла вентшахта АБК</t>
+          <t>З південного краю аркового даху АБК на захід: ліворуч парапет, нижче — дах південного блоку АБК і ТП-5913, бетонна стіна цеху з вікнами; над нею дах цеху — рама кондиціонерів, дефлектори, ліхтарі. Кругла вентшахта АБК</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O87" s="7" t="inlineStr">
@@ -6538,14 +6538,14 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>315</v>
@@ -6558,7 +6558,7 @@
       <c r="M88" s="4" t="inlineStr"/>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I89" s="7" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K89" s="7" t="n">
         <v>335</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>Уздовж даху АБК на північ, ліворуч стіна цеху; вентшахти</t>
+          <t>Уздовж аркового даху АБК на північ (гребінь уздовж Пн–Пд), ліворуч — бетонна стіна цеху за проїздом; вентшахти</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O89" s="7" t="inlineStr">
@@ -6678,27 +6678,27 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>350</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>Уздовж даху АБК на північ: вентшахти, вдалині житлова вежа</t>
+          <t>Уздовж аркового даху АБК на північ: дах опуклий, ринви біля парапетів; вентшахти, вдалині житлова вежа</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
@@ -6748,14 +6748,14 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I91" s="7" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K91" s="7" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
       <c r="M91" s="7" t="inlineStr"/>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O91" s="7" t="inlineStr">
@@ -6818,14 +6818,14 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>15</v>
@@ -6838,7 +6838,7 @@
       <c r="M92" s="4" t="inlineStr"/>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -6888,14 +6888,14 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I93" s="7" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K93" s="7" t="n">
         <v>35</v>
@@ -6908,7 +6908,7 @@
       <c r="M93" s="7" t="inlineStr"/>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
@@ -6958,14 +6958,14 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>60</v>
@@ -6978,7 +6978,7 @@
       <c r="M94" s="4" t="inlineStr"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -7028,14 +7028,14 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I95" s="7" t="n">
-        <v>112</v>
+        <v>117.5</v>
       </c>
       <c r="J95" s="7" t="n">
-        <v>-3</v>
+        <v>21.8</v>
       </c>
       <c r="K95" s="7" t="n">
         <v>100</v>
@@ -7048,7 +7048,7 @@
       <c r="M95" s="7" t="inlineStr"/>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O95" s="7" t="inlineStr">
@@ -7098,14 +7098,14 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>2</v>
+        <v>25.9</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>0</v>
@@ -7118,7 +7118,7 @@
       <c r="M96" s="4" t="inlineStr"/>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -7168,14 +7168,14 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>2</v>
+        <v>25.9</v>
       </c>
       <c r="K97" s="7" t="n">
         <v>5</v>
@@ -7188,7 +7188,7 @@
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O97" s="7" t="inlineStr">
@@ -7238,14 +7238,14 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>2</v>
+        <v>25.9</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>10</v>
@@ -7258,7 +7258,7 @@
       <c r="M98" s="4" t="inlineStr"/>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I99" s="7" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K99" s="7" t="n">
         <v>20</v>
@@ -7328,7 +7328,7 @@
       <c r="M99" s="7" t="inlineStr"/>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O99" s="7" t="inlineStr">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>45</v>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="I101" s="7" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K101" s="7" t="n">
         <v>90</v>
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>120</v>
@@ -7588,14 +7588,14 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I103" s="7" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>150</v>
@@ -7608,7 +7608,7 @@
       <c r="M103" s="7" t="inlineStr"/>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O103" s="7" t="inlineStr">
@@ -7658,14 +7658,14 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>170</v>
@@ -7678,7 +7678,7 @@
       <c r="M104" s="4" t="inlineStr"/>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -7728,14 +7728,14 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I105" s="7" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J105" s="7" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K105" s="7" t="n">
         <v>190</v>
@@ -7748,7 +7748,7 @@
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O105" s="7" t="inlineStr">
@@ -7798,14 +7798,14 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>6</v>
+        <v>29.1</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>215</v>
@@ -7818,7 +7818,7 @@
       <c r="M106" s="4" t="inlineStr"/>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>116</v>
+        <v>116.9</v>
       </c>
       <c r="J107" s="7" t="n">
-        <v>8</v>
+        <v>30.7</v>
       </c>
       <c r="K107" s="7" t="n">
         <v>250</v>
@@ -7888,7 +7888,7 @@
       <c r="M107" s="7" t="inlineStr"/>
       <c r="N107" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O107" s="7" t="inlineStr">
@@ -7938,14 +7938,14 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>116</v>
+        <v>116.9</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>8</v>
+        <v>30.7</v>
       </c>
       <c r="K108" s="4" t="n">
         <v>275</v>
@@ -7958,7 +7958,7 @@
       <c r="M108" s="4" t="inlineStr"/>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8008,14 +8008,14 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>116</v>
+        <v>116.9</v>
       </c>
       <c r="J109" s="7" t="n">
-        <v>8</v>
+        <v>30.7</v>
       </c>
       <c r="K109" s="7" t="n">
         <v>290</v>
@@ -8028,7 +8028,7 @@
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O109" s="7" t="inlineStr">
@@ -8078,14 +8078,14 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>123</v>
+        <v>126.6</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>10</v>
+        <v>32.3</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>120</v>
@@ -8098,7 +8098,7 @@
       <c r="M110" s="4" t="inlineStr"/>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -8148,14 +8148,14 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>122</v>
+        <v>125.2</v>
       </c>
       <c r="J111" s="7" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K111" s="7" t="n">
         <v>100</v>
@@ -8168,7 +8168,7 @@
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O111" s="7" t="inlineStr">
@@ -8218,14 +8218,14 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>122</v>
+        <v>115.4</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>12</v>
+        <v>44.4</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>120</v>
@@ -8238,7 +8238,7 @@
       <c r="M112" s="4" t="inlineStr"/>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -8288,14 +8288,14 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>122</v>
+        <v>115.4</v>
       </c>
       <c r="J113" s="7" t="n">
-        <v>12</v>
+        <v>44.4</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>150</v>
@@ -8308,7 +8308,7 @@
       <c r="M113" s="7" t="inlineStr"/>
       <c r="N113" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O113" s="7" t="inlineStr">
@@ -8358,14 +8358,14 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>122</v>
+        <v>115.4</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>12</v>
+        <v>44.4</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>175</v>
@@ -8378,7 +8378,7 @@
       <c r="M114" s="4" t="inlineStr"/>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>120</v>
+        <v>117.6</v>
       </c>
       <c r="J115" s="7" t="n">
-        <v>14</v>
+        <v>44.2</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>200</v>
@@ -8448,7 +8448,7 @@
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O115" s="7" t="inlineStr">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>120</v>
+        <v>117.6</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>14</v>
+        <v>44.2</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>215</v>
@@ -8518,7 +8518,7 @@
       <c r="M116" s="4" t="inlineStr"/>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -8568,14 +8568,14 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I117" s="7" t="n">
-        <v>120</v>
+        <v>117.6</v>
       </c>
       <c r="J117" s="7" t="n">
-        <v>14</v>
+        <v>44.2</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>235</v>
@@ -8588,7 +8588,7 @@
       <c r="M117" s="7" t="inlineStr"/>
       <c r="N117" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O117" s="7" t="inlineStr">
@@ -8638,14 +8638,14 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>120</v>
+        <v>117.6</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>14</v>
+        <v>44.2</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>255</v>
@@ -8658,7 +8658,7 @@
       <c r="M118" s="4" t="inlineStr"/>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -8708,14 +8708,14 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I119" s="7" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J119" s="7" t="n">
-        <v>16</v>
+        <v>37.2</v>
       </c>
       <c r="K119" s="7" t="n">
         <v>280</v>
@@ -8728,7 +8728,7 @@
       <c r="M119" s="7" t="inlineStr"/>
       <c r="N119" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O119" s="7" t="inlineStr">
@@ -8778,14 +8778,14 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>118</v>
+        <v>119.6</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>16</v>
+        <v>37.2</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>295</v>
@@ -8798,7 +8798,7 @@
       <c r="M120" s="4" t="inlineStr"/>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -8848,14 +8848,14 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I121" s="7" t="n">
-        <v>111</v>
+        <v>110.5</v>
       </c>
       <c r="J121" s="7" t="n">
-        <v>20</v>
+        <v>43.5</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>300</v>
@@ -8868,7 +8868,7 @@
       <c r="M121" s="7" t="inlineStr"/>
       <c r="N121" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O121" s="7" t="inlineStr">
@@ -8918,14 +8918,14 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>111</v>
+        <v>112.3</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>340</v>
@@ -8938,7 +8938,7 @@
       <c r="M122" s="4" t="inlineStr"/>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I123" s="7" t="n">
-        <v>111</v>
+        <v>110.5</v>
       </c>
       <c r="J123" s="7" t="n">
-        <v>20</v>
+        <v>43.5</v>
       </c>
       <c r="K123" s="7" t="n">
         <v>190</v>
@@ -9008,7 +9008,7 @@
       <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O123" s="7" t="inlineStr">
@@ -9058,14 +9058,14 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>124</v>
+        <v>127.6</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>8</v>
+        <v>30.7</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>90</v>
@@ -9078,7 +9078,7 @@
       <c r="M124" s="4" t="inlineStr"/>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9128,14 +9128,14 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I125" s="7" t="n">
-        <v>124</v>
+        <v>127.6</v>
       </c>
       <c r="J125" s="7" t="n">
-        <v>8</v>
+        <v>30.7</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>80</v>
@@ -9148,7 +9148,7 @@
       <c r="M125" s="7" t="inlineStr"/>
       <c r="N125" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O125" s="7" t="inlineStr">
@@ -9198,14 +9198,14 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>123</v>
+        <v>126.6</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>190</v>
@@ -9218,7 +9218,7 @@
       <c r="M126" s="4" t="inlineStr"/>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -9268,14 +9268,14 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I127" s="7" t="n">
-        <v>123</v>
+        <v>126.6</v>
       </c>
       <c r="J127" s="7" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>190</v>
@@ -9288,7 +9288,7 @@
       <c r="M127" s="7" t="inlineStr"/>
       <c r="N127" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O127" s="7" t="inlineStr">
@@ -9338,27 +9338,27 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>121</v>
+        <v>118.9</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>20</v>
+        <v>44.4</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>220</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>Дві супутникові антени, вентвихід</t>
+          <t>Високий і низький (напівкруглий) оцинковані вентвиходи, кругла вентшахта, вдалині димар (27.10 помилково підписано «дві супутникові антени»)</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr"/>
       <c r="N128" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -9408,14 +9408,14 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I129" s="7" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J129" s="7" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K129" s="7" t="n">
         <v>255</v>
@@ -9428,7 +9428,7 @@
       <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -9478,14 +9478,14 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>265</v>
@@ -9498,7 +9498,7 @@
       <c r="M130" s="4" t="inlineStr"/>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -9548,14 +9548,14 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I131" s="7" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J131" s="7" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>285</v>
@@ -9568,7 +9568,7 @@
       <c r="M131" s="7" t="inlineStr"/>
       <c r="N131" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O131" s="7" t="inlineStr">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>300</v>
@@ -9638,7 +9638,7 @@
       <c r="M132" s="4" t="inlineStr"/>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -9688,14 +9688,14 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J133" s="7" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K133" s="7" t="n">
         <v>310</v>
@@ -9708,7 +9708,7 @@
       <c r="M133" s="7" t="inlineStr"/>
       <c r="N133" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O133" s="7" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I134" s="10" t="n"/>
@@ -9772,7 +9772,7 @@
       <c r="M134" s="10" t="inlineStr"/>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -9822,14 +9822,14 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
         </is>
       </c>
       <c r="I135" s="7" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="J135" s="7" t="n">
-        <v>8</v>
+        <v>40.9</v>
       </c>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="12" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O135" s="7" t="inlineStr">
@@ -9894,27 +9894,27 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>200</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>Униз на нижчий плаский дах між АБК і цехом (ймовірно ТП-5913): воронки, праворуч стіна цеху з вікнами</t>
+          <t>Униз на плаский дах південного блоку АБК (3 пов.): воронка, розмітка; праворуч за проїздом — дах ТП-5913 і бетонна стіна цеху з вікнами</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr"/>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
@@ -9964,27 +9964,27 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J137" s="7" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="K137" s="7" t="n">
         <v>210</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>Нижній дах: воронки, цегляна надбудова з пласким дахом, біла вертикальна труба. На Диску 2 однакові копії · на Диску 2 однакові копії</t>
+          <t>Дах південного блоку АБК: воронки, цегляна надбудова сходів, біла вертикальна труба. На Диску 2 однакові копії · на Диску 2 однакові копії</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O137" s="7" t="inlineStr">
@@ -10034,27 +10034,27 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>220</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>Цегляна надбудова на нижньому даху</t>
+          <t>Цегляна надбудова сходів на даху південного блоку АБК</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr"/>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O138" s="4" t="inlineStr">
@@ -10104,14 +10104,14 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J139" s="7" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>230</v>
@@ -10124,7 +10124,7 @@
       <c r="M139" s="7" t="inlineStr"/>
       <c r="N139" s="7" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O139" s="7" t="inlineStr">
@@ -10174,14 +10174,14 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>240</v>
@@ -10194,7 +10194,7 @@
       <c r="M140" s="4" t="inlineStr"/>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>є умовно</t>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
@@ -15531,22 +15531,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Адмінкорпус (АБК) — дах</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>є умовно</t>
+          <t>Адмінкорпус (АБК) — основний блок, арковий дах</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Додано: парапет, 5 круглих вентшахт, високий і низький вентвиходи, 2 антени, пруток блискавкозахисту — положення оцінка ±5–10 м.</t>
+          <t>Виправлено ввечері 27.10: план за супутником Google — 19,5 × 24,9 м (X 108,5–128,0, Y 20,3–45,2; було 14 × 31 м зі зсувом на 11 м на південь); дах арковий уздовж Пн–Пд, стріла ≈1,3 м (оцінка); 5 вентшахт і 2 вентвиходи — за супутником і фото; «2 антени» прибрано — це вентвиходи.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>З даху АБК видно покрівлю цеху над його парапетом — отже, дах АБК вищий за 13,2 м у моделі (ймовірно ≈15 м). Виміряти висоту і розміри АБК, якщо дах АБК розглядаємо під модулі.</t>
+          <t>Виміряти: висоту карниза або перепад від парапету цеху до ринви АБК, стрілу арки (рулетка від ринви до гребеня), висоту парапетів.</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Точки фото 27.10 додано.</t>
+          <t>Точки фото 27.10 додано; план — супутник 27.10.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>На фото з двору — 3 поверхи вікон над цоколем + парапет, вхід із козирком. Розміри не виміряні.</t>
+          <t>Південний блок — 3 поверхи, основний — 4 (за фото); висоти поверхів не виміряні.</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -15601,22 +15601,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Нижній плаский дах між АБК і цехом (ймовірно ТП-5913)</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>є умовно</t>
+          <t>Південний блок АБК — плаский дах із надбудовою сходів</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>є (план — супутник)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Виправлено ввечері 27.10: це не ТП-5913, а нижній (3 пов.) блок АБК 19,2 × 13,7 м із цегляною надбудовою сходів 5,2 × 9,8 м.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Воронки, цегляна надбудова, біла вертикальна труба — немає. Уточнити, що це за будівля.</t>
+          <t>Воронки, біла вертикальна труба — не нанесено. Висота ≈10 м — оцінка.</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
